--- a/Lab/outils/input/source.xlsx
+++ b/Lab/outils/input/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a386a22b2d8d1dbd/000 CINE CARBONNE 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Boulots\Cine Carbonne\Site\Site_Github_rep\Lab\outils\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1323" documentId="8_{D20FCBFB-1DAC-428D-B54C-5B28F5E5D113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D8D96FF-A65A-4BAE-B9C2-FC506616133F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B735A55-DDEF-4DA6-B232-AAB68EFF267E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="587" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13740" tabRatio="587" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -513,9 +513,6 @@
     <t xml:space="preserve">Love on trial </t>
   </si>
   <si>
-    <t>Woman and child VO</t>
-  </si>
-  <si>
     <t xml:space="preserve">Il maestro </t>
   </si>
   <si>
@@ -775,6 +772,9 @@
   </si>
   <si>
     <t>DOC Coup de coeur</t>
+  </si>
+  <si>
+    <t>Woman and child</t>
   </si>
 </sst>
 </file>
@@ -1910,9 +1910,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1950,7 +1950,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2056,7 +2056,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2198,7 +2198,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2210,25 +2210,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O114"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.88671875" style="201" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" style="201" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" customWidth="1"/>
     <col min="4" max="4" width="5" style="114" customWidth="1"/>
-    <col min="5" max="5" width="69.5546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" style="85" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="33.5546875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="79.109375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="35.21875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="20.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="69.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="85" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="33.5703125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="79.140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="35.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" style="2" customWidth="1"/>
     <col min="12" max="12" width="54" style="2" customWidth="1"/>
-    <col min="13" max="13" width="59.21875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="92.5546875" customWidth="1"/>
-    <col min="15" max="15" width="43.88671875" customWidth="1"/>
+    <col min="13" max="13" width="59.28515625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="92.5703125" customWidth="1"/>
+    <col min="15" max="15" width="43.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="E1" s="102"/>
       <c r="F1" s="103"/>
       <c r="G1" s="104"/>
@@ -2238,7 +2238,7 @@
       <c r="K1" s="192"/>
       <c r="L1" s="102"/>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="15.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="202"/>
       <c r="D2" s="115"/>
       <c r="E2" s="102"/>
@@ -2251,7 +2251,7 @@
       <c r="L2" s="102"/>
       <c r="M2" s="6"/>
     </row>
-    <row r="3" spans="1:14" s="71" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" s="71" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="202"/>
       <c r="D3" s="116"/>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="M3" s="74"/>
     </row>
-    <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="203" t="s">
         <v>0</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="205" t="s">
         <v>1</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="27"/>
       <c r="B6" s="207"/>
       <c r="C6" s="14"/>
@@ -2349,7 +2349,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="27"/>
       <c r="B7" s="207"/>
       <c r="C7" s="14"/>
@@ -2369,7 +2369,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41"/>
       <c r="B8" s="208"/>
       <c r="C8" s="16" t="s">
@@ -2384,13 +2384,13 @@
       </c>
       <c r="G8" s="37"/>
       <c r="H8" s="183" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I8" s="37" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J8" s="43" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K8" s="18"/>
       <c r="L8" s="100"/>
@@ -2401,7 +2401,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="209" t="s">
         <v>2</v>
       </c>
@@ -2425,30 +2425,30 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="56"/>
       <c r="B10" s="207"/>
       <c r="C10" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D10" s="128"/>
       <c r="E10" s="190" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F10" s="83"/>
       <c r="G10" s="67"/>
       <c r="H10" s="67"/>
       <c r="I10" s="67" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J10" s="45" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K10" s="191">
         <v>2.8</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M10" s="22" t="s">
         <v>132</v>
@@ -2457,7 +2457,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="56"/>
       <c r="B11" s="210"/>
       <c r="C11" s="14"/>
@@ -2477,7 +2477,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41"/>
       <c r="B12" s="208"/>
       <c r="C12" s="16" t="s">
@@ -2492,13 +2492,13 @@
       </c>
       <c r="G12" s="40"/>
       <c r="H12" s="183" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I12" s="78" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J12" s="43" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K12" s="18"/>
       <c r="L12" s="100"/>
@@ -2509,7 +2509,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="209" t="s">
         <v>4</v>
       </c>
@@ -2517,26 +2517,26 @@
         <v>46101</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="194" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F13" s="135"/>
       <c r="G13" s="24"/>
       <c r="H13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I13"/>
       <c r="J13" s="46" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K13" s="191">
         <v>2.8</v>
       </c>
       <c r="L13" s="24" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M13" s="20" t="s">
         <v>84</v>
@@ -2545,7 +2545,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25"/>
       <c r="B14" s="210"/>
       <c r="C14" s="14" t="s">
@@ -2558,7 +2558,7 @@
       <c r="F14" s="136"/>
       <c r="G14" s="32"/>
       <c r="H14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I14" s="54"/>
       <c r="J14" s="40" t="s">
@@ -2575,7 +2575,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="27"/>
       <c r="B15" s="210"/>
       <c r="C15" s="14"/>
@@ -2595,7 +2595,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="41"/>
       <c r="B16" s="208"/>
       <c r="C16" s="16" t="s">
@@ -2613,7 +2613,7 @@
         <v>129</v>
       </c>
       <c r="I16" s="40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J16" s="181" t="s">
         <v>130</v>
@@ -2627,7 +2627,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="209" t="s">
         <v>5</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="56"/>
       <c r="B18" s="207"/>
       <c r="C18" s="14" t="s">
@@ -2664,7 +2664,7 @@
       <c r="F18" s="130"/>
       <c r="G18" s="37"/>
       <c r="H18" s="25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I18" s="37"/>
       <c r="J18" s="45" t="s">
@@ -2681,7 +2681,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="56"/>
       <c r="B19" s="210"/>
       <c r="C19" s="14" t="s">
@@ -2694,7 +2694,7 @@
       <c r="F19" s="83"/>
       <c r="G19" s="67"/>
       <c r="H19" s="67" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I19" s="67" t="s">
         <v>138</v>
@@ -2713,7 +2713,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41"/>
       <c r="B20" s="208"/>
       <c r="C20" s="16" t="s">
@@ -2728,13 +2728,13 @@
       </c>
       <c r="G20" s="37"/>
       <c r="H20" s="37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J20" s="47" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K20" s="18"/>
       <c r="L20" s="110"/>
@@ -2743,7 +2743,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="209" t="s">
         <v>7</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="56"/>
       <c r="B22" s="207"/>
       <c r="C22" s="14" t="s">
@@ -2778,7 +2778,7 @@
       <c r="F22" s="130"/>
       <c r="G22" s="37"/>
       <c r="H22" s="37" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I22" s="37"/>
       <c r="J22" s="45" t="s">
@@ -2791,7 +2791,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="56"/>
       <c r="B23" s="210"/>
       <c r="C23" s="14" t="s">
@@ -2804,7 +2804,7 @@
       <c r="F23" s="130"/>
       <c r="G23" s="37"/>
       <c r="H23" s="37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I23" s="37"/>
       <c r="J23" s="45"/>
@@ -2815,7 +2815,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="41"/>
       <c r="B24" s="208"/>
       <c r="C24" s="17"/>
@@ -2833,7 +2833,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="209" t="s">
         <v>8</v>
       </c>
@@ -2841,33 +2841,33 @@
         <v>46104</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="195" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F25" s="144"/>
       <c r="G25" s="19"/>
       <c r="H25" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I25" s="44"/>
       <c r="J25" s="44" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K25" s="196">
         <v>4</v>
       </c>
       <c r="L25" s="19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M25" s="26"/>
       <c r="N25" s="123" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="110"/>
       <c r="B26" s="211"/>
       <c r="C26" s="16"/>
@@ -2885,7 +2885,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="31" t="s">
         <v>9</v>
       </c>
@@ -2905,7 +2905,7 @@
       <c r="M27" s="22"/>
       <c r="N27" s="26"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="56"/>
       <c r="B28" s="207"/>
       <c r="C28" s="14"/>
@@ -2921,7 +2921,7 @@
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
     </row>
-    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="56"/>
       <c r="B29" s="210"/>
       <c r="C29" s="14"/>
@@ -2937,7 +2937,7 @@
       <c r="M29" s="27"/>
       <c r="N29" s="22"/>
     </row>
-    <row r="30" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="41"/>
       <c r="B30" s="208"/>
       <c r="C30" s="16" t="s">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="G30" s="40"/>
       <c r="H30" s="40" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I30" s="40"/>
       <c r="J30" s="43"/>
@@ -2961,7 +2961,7 @@
       <c r="M30" s="58"/>
       <c r="N30" s="22"/>
     </row>
-    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="203" t="s">
         <v>0</v>
       </c>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="N31" s="61"/>
     </row>
-    <row r="32" spans="1:14" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="209" t="s">
         <v>1</v>
       </c>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="N32" s="25"/>
     </row>
-    <row r="33" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="56"/>
       <c r="B33" s="210"/>
       <c r="C33" s="14"/>
@@ -3025,7 +3025,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="56"/>
       <c r="B34" s="210"/>
       <c r="C34" s="14"/>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="N34" s="177"/>
     </row>
-    <row r="35" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="41"/>
       <c r="B35" s="208"/>
       <c r="C35" s="16" t="s">
@@ -3056,11 +3056,11 @@
       <c r="F35" s="134"/>
       <c r="G35" s="40"/>
       <c r="H35" s="40" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I35" s="40"/>
       <c r="J35" s="97" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K35" s="77"/>
       <c r="L35" s="77"/>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="N35" s="61"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="209" t="s">
         <v>2</v>
       </c>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="N36" s="25"/>
     </row>
-    <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="56"/>
       <c r="B37" s="210"/>
       <c r="C37" s="35"/>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="N37" s="61"/>
     </row>
-    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="56"/>
       <c r="B38" s="210"/>
       <c r="C38" s="35"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="N38" s="26"/>
     </row>
-    <row r="39" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="41"/>
       <c r="B39" s="208"/>
       <c r="C39" s="16" t="s">
@@ -3142,11 +3142,11 @@
       </c>
       <c r="G39" s="40"/>
       <c r="H39" s="183" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I39" s="40"/>
       <c r="J39" s="97" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K39" s="77"/>
       <c r="L39" s="77"/>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="N39" s="25"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="209" t="s">
         <v>4</v>
       </c>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="N40" s="65"/>
     </row>
-    <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="56"/>
       <c r="B41" s="210"/>
       <c r="C41" s="35"/>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="N41" s="61"/>
     </row>
-    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="56"/>
       <c r="B42" s="210"/>
       <c r="C42" s="14"/>
@@ -3214,7 +3214,7 @@
       <c r="N42" s="177"/>
       <c r="O42" s="5"/>
     </row>
-    <row r="43" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="41"/>
       <c r="B43" s="208"/>
       <c r="C43" s="33" t="s">
@@ -3229,13 +3229,13 @@
       </c>
       <c r="G43" s="40"/>
       <c r="H43" s="37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I43" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J43" s="97" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K43" s="77"/>
       <c r="L43" s="99"/>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="N43" s="22"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="209" t="s">
         <v>5</v>
       </c>
@@ -3267,7 +3267,7 @@
       <c r="N44" s="26"/>
       <c r="O44" s="4"/>
     </row>
-    <row r="45" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="56"/>
       <c r="B45" s="210"/>
       <c r="C45" s="35" t="s">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="D45" s="154"/>
       <c r="E45" s="27" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F45" s="155"/>
       <c r="G45" s="156"/>
       <c r="H45" s="25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I45" s="156"/>
       <c r="J45" s="45" t="s">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="N45" s="61"/>
     </row>
-    <row r="46" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="56"/>
       <c r="B46" s="210"/>
       <c r="C46" s="35" t="s">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="G46" s="67"/>
       <c r="H46" s="67" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I46" s="67"/>
       <c r="J46" s="38" t="s">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="N46" s="61"/>
     </row>
-    <row r="47" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="41"/>
       <c r="B47" s="208"/>
       <c r="C47" s="16" t="s">
@@ -3340,7 +3340,7 @@
       <c r="F47" s="157"/>
       <c r="G47" s="99"/>
       <c r="H47" s="158" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I47" s="159"/>
       <c r="J47" s="39"/>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="N47" s="177"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="209" t="s">
         <v>7</v>
       </c>
@@ -3359,31 +3359,31 @@
         <v>46110</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="188" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F48" s="189"/>
       <c r="G48" s="25"/>
       <c r="H48" s="25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I48" s="161"/>
       <c r="J48" s="25" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K48" s="177"/>
       <c r="L48" s="25" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M48" s="61" t="s">
         <v>131</v>
       </c>
       <c r="N48" s="25"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="56"/>
       <c r="B49" s="210"/>
       <c r="C49" s="35" t="s">
@@ -3396,7 +3396,7 @@
       <c r="F49" s="83"/>
       <c r="G49" s="67"/>
       <c r="H49" s="67" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I49" s="67"/>
       <c r="J49" s="38" t="s">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="N49" s="61"/>
     </row>
-    <row r="50" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="56"/>
       <c r="B50" s="210"/>
       <c r="C50" s="35" t="s">
@@ -3422,7 +3422,7 @@
       <c r="F50" s="130"/>
       <c r="G50" s="37"/>
       <c r="H50" s="37" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I50" s="22"/>
       <c r="J50" s="98"/>
@@ -3431,7 +3431,7 @@
       <c r="M50" s="22"/>
       <c r="N50" s="61"/>
     </row>
-    <row r="51" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="41"/>
       <c r="B51" s="208"/>
       <c r="C51" s="16"/>
@@ -3449,7 +3449,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="209" t="s">
         <v>8</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="110"/>
       <c r="B53" s="211"/>
       <c r="C53" s="16"/>
@@ -3489,7 +3489,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="31" t="s">
         <v>9</v>
       </c>
@@ -3509,24 +3509,24 @@
       <c r="M54" s="22"/>
       <c r="N54" s="21"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="56"/>
       <c r="B55" s="207"/>
       <c r="C55" s="14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D55" s="128"/>
       <c r="E55" s="197" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F55" s="146"/>
       <c r="G55" s="147"/>
       <c r="H55" s="67" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I55" s="147"/>
       <c r="J55" s="45" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K55" s="191">
         <v>3.5</v>
@@ -3535,7 +3535,7 @@
       <c r="M55" s="22"/>
       <c r="N55" s="108"/>
     </row>
-    <row r="56" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="56"/>
       <c r="B56" s="210"/>
       <c r="C56" s="14"/>
@@ -3551,7 +3551,7 @@
       <c r="M56" s="27"/>
       <c r="N56" s="92"/>
     </row>
-    <row r="57" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="41"/>
       <c r="B57" s="208"/>
       <c r="C57" s="16" t="s">
@@ -3564,7 +3564,7 @@
       <c r="F57" s="134"/>
       <c r="G57" s="40"/>
       <c r="H57" s="165" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I57" s="40"/>
       <c r="J57" s="43"/>
@@ -3573,7 +3573,7 @@
       <c r="M57" s="58"/>
       <c r="N57" s="91"/>
     </row>
-    <row r="58" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="203" t="s">
         <v>0</v>
       </c>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="N58" s="92"/>
     </row>
-    <row r="59" spans="1:14" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="209" t="s">
         <v>1</v>
       </c>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="N59" s="21"/>
     </row>
-    <row r="60" spans="1:14" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="56"/>
       <c r="B60" s="210"/>
       <c r="C60" s="14"/>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="N60" s="90"/>
     </row>
-    <row r="61" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="56"/>
       <c r="B61" s="210"/>
       <c r="C61" s="14"/>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="N61" s="90"/>
     </row>
-    <row r="62" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="41"/>
       <c r="B62" s="208"/>
       <c r="C62" s="33" t="s">
@@ -3668,11 +3668,11 @@
       </c>
       <c r="G62" s="40"/>
       <c r="H62" s="183" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I62" s="40"/>
       <c r="J62" s="97" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K62" s="77"/>
       <c r="L62" s="99"/>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="N62" s="27"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="209" t="s">
         <v>2</v>
       </c>
@@ -3705,7 +3705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="56"/>
       <c r="B64" s="210"/>
       <c r="C64" s="35"/>
@@ -3725,7 +3725,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="56"/>
       <c r="B65" s="210"/>
       <c r="C65" s="35"/>
@@ -3745,7 +3745,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="41"/>
       <c r="B66" s="208"/>
       <c r="C66" s="16" t="s">
@@ -3760,11 +3760,11 @@
       </c>
       <c r="G66" s="40"/>
       <c r="H66" s="40" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I66" s="40"/>
       <c r="J66" s="97" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K66" s="77"/>
       <c r="L66" s="77"/>
@@ -3775,7 +3775,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="209" t="s">
         <v>4</v>
       </c>
@@ -3799,7 +3799,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="56"/>
       <c r="B68" s="210"/>
       <c r="C68" s="14" t="s">
@@ -3812,7 +3812,7 @@
       <c r="F68" s="136"/>
       <c r="G68" s="54"/>
       <c r="H68" s="54" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I68" s="54"/>
       <c r="J68" s="40" t="s">
@@ -3829,7 +3829,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="56"/>
       <c r="B69" s="210"/>
       <c r="C69" s="14"/>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O69" s="5"/>
     </row>
-    <row r="70" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="41"/>
       <c r="B70" s="208"/>
       <c r="C70" s="33" t="s">
@@ -3865,11 +3865,11 @@
       </c>
       <c r="G70" s="40"/>
       <c r="H70" s="40" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I70" s="40"/>
       <c r="J70" s="97" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K70" s="77"/>
       <c r="L70" s="99"/>
@@ -3880,7 +3880,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="213" t="s">
         <v>5</v>
       </c>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="O71" s="4"/>
     </row>
-    <row r="72" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="215"/>
       <c r="B72" s="216"/>
       <c r="C72" s="14" t="s">
@@ -3918,14 +3918,14 @@
       <c r="F72" s="155"/>
       <c r="G72" s="156"/>
       <c r="H72" s="156" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I72" s="156"/>
       <c r="J72" s="37" t="s">
         <v>36</v>
       </c>
       <c r="K72" s="22" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L72" s="22"/>
       <c r="M72" s="124" t="s">
@@ -3935,7 +3935,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="215"/>
       <c r="B73" s="216"/>
       <c r="C73" s="14" t="s">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="G73" s="67"/>
       <c r="H73" s="67" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I73" s="67"/>
       <c r="J73" s="37" t="s">
@@ -3967,7 +3967,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="217"/>
       <c r="B74" s="218"/>
       <c r="C74" s="16" t="s">
@@ -3980,7 +3980,7 @@
       <c r="F74" s="167"/>
       <c r="G74" s="159"/>
       <c r="H74" s="158" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I74" s="158"/>
       <c r="J74" s="39"/>
@@ -3989,7 +3989,7 @@
       <c r="M74" s="61"/>
       <c r="N74" s="61"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="213" t="s">
         <v>7</v>
       </c>
@@ -4009,7 +4009,7 @@
       <c r="M75" s="61"/>
       <c r="N75" s="22"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="215"/>
       <c r="B76" s="216"/>
       <c r="C76" s="35" t="s">
@@ -4022,7 +4022,7 @@
       <c r="F76" s="83"/>
       <c r="G76" s="67"/>
       <c r="H76" s="67" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I76" s="67"/>
       <c r="J76" s="38" t="s">
@@ -4033,7 +4033,7 @@
       <c r="M76" s="27"/>
       <c r="N76" s="56"/>
     </row>
-    <row r="77" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="215"/>
       <c r="B77" s="216"/>
       <c r="C77" s="35" t="s">
@@ -4046,7 +4046,7 @@
       <c r="F77" s="130"/>
       <c r="G77" s="37"/>
       <c r="H77" s="37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I77" s="37"/>
       <c r="J77" s="98"/>
@@ -4055,7 +4055,7 @@
       <c r="M77" s="22"/>
       <c r="N77" s="65"/>
     </row>
-    <row r="78" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="217"/>
       <c r="B78" s="218"/>
       <c r="C78" s="16" t="s">
@@ -4068,7 +4068,7 @@
       <c r="F78" s="163"/>
       <c r="G78" s="140"/>
       <c r="H78" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I78" s="140"/>
       <c r="J78" s="41"/>
@@ -4077,7 +4077,7 @@
       <c r="M78" s="26"/>
       <c r="N78" s="27"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="213" t="s">
         <v>8</v>
       </c>
@@ -4094,7 +4094,7 @@
       <c r="F79" s="144"/>
       <c r="G79" s="44"/>
       <c r="H79" s="44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I79" s="44"/>
       <c r="J79" s="44"/>
@@ -4103,7 +4103,7 @@
       <c r="M79" s="26"/>
       <c r="N79" s="22"/>
     </row>
-    <row r="80" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="219"/>
       <c r="B80" s="220"/>
       <c r="C80" s="16"/>
@@ -4119,7 +4119,7 @@
       <c r="M80" s="26"/>
       <c r="N80" s="22"/>
     </row>
-    <row r="81" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="31" t="s">
         <v>9</v>
       </c>
@@ -4139,39 +4139,39 @@
       <c r="M81" s="22"/>
       <c r="N81" s="21"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="56"/>
       <c r="B82" s="207"/>
       <c r="C82" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D82" s="128"/>
       <c r="E82" s="199" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F82" s="150" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G82" s="147"/>
       <c r="H82" s="52" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I82" s="147"/>
       <c r="J82" s="45" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K82" s="200">
         <v>4</v>
       </c>
       <c r="L82" s="21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M82" s="22"/>
       <c r="N82" s="96" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="56"/>
       <c r="B83" s="210"/>
       <c r="C83" s="14"/>
@@ -4187,7 +4187,7 @@
       <c r="M83" s="27"/>
       <c r="N83" s="88"/>
     </row>
-    <row r="84" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="41"/>
       <c r="B84" s="208"/>
       <c r="C84" s="16" t="s">
@@ -4195,25 +4195,25 @@
       </c>
       <c r="D84" s="17"/>
       <c r="E84" s="22" t="s">
-        <v>159</v>
+        <v>246</v>
       </c>
       <c r="F84" s="134" t="s">
         <v>35</v>
       </c>
       <c r="G84" s="40"/>
       <c r="H84" s="40" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I84" s="40"/>
       <c r="J84" s="43" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K84" s="18"/>
       <c r="L84" s="18"/>
       <c r="M84" s="58"/>
       <c r="N84" s="25"/>
     </row>
-    <row r="85" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="203" t="s">
         <v>0</v>
       </c>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="N85" s="25"/>
     </row>
-    <row r="86" spans="1:15" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="209" t="s">
         <v>1</v>
       </c>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="N86" s="25"/>
     </row>
-    <row r="87" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="56"/>
       <c r="B87" s="210"/>
       <c r="C87" s="14"/>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="N87" s="25"/>
     </row>
-    <row r="88" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="56"/>
       <c r="B88" s="210"/>
       <c r="C88" s="35"/>
@@ -4291,7 +4291,7 @@
       <c r="M88" s="60"/>
       <c r="N88" s="25"/>
     </row>
-    <row r="89" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="41"/>
       <c r="B89" s="208"/>
       <c r="C89" s="33" t="s">
@@ -4306,11 +4306,11 @@
       </c>
       <c r="G89" s="40"/>
       <c r="H89" s="40" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I89" s="40"/>
       <c r="J89" s="97" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K89" s="77"/>
       <c r="L89" s="15"/>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="N89" s="25"/>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="209" t="s">
         <v>2</v>
       </c>
@@ -4341,30 +4341,30 @@
       </c>
       <c r="N90" s="87"/>
     </row>
-    <row r="91" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="56"/>
       <c r="B91" s="210"/>
       <c r="C91" s="35" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D91" s="128"/>
       <c r="E91" s="198" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F91" s="130"/>
       <c r="G91" s="37"/>
       <c r="H91" s="37" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I91" s="37"/>
       <c r="J91" s="54" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K91" s="200">
         <v>4</v>
       </c>
       <c r="L91" s="21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M91" s="22" t="s">
         <v>118</v>
@@ -4373,7 +4373,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="56"/>
       <c r="B92" s="210"/>
       <c r="D92" s="128"/>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="N92" s="65"/>
     </row>
-    <row r="93" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="41"/>
       <c r="B93" s="208"/>
       <c r="C93" s="16" t="s">
@@ -4405,11 +4405,11 @@
       </c>
       <c r="G93" s="40"/>
       <c r="H93" s="40" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I93" s="40"/>
       <c r="J93" s="97" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K93" s="77"/>
       <c r="L93" s="15"/>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="N93" s="25"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="209" t="s">
         <v>4</v>
       </c>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="N94" s="65"/>
     </row>
-    <row r="95" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="56"/>
       <c r="B95" s="210"/>
       <c r="C95" s="35"/>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="N95" s="25"/>
     </row>
-    <row r="96" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="56"/>
       <c r="B96" s="210"/>
       <c r="C96" s="14"/>
@@ -4477,7 +4477,7 @@
       <c r="N96" s="65"/>
       <c r="O96" s="5"/>
     </row>
-    <row r="97" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="41"/>
       <c r="B97" s="208"/>
       <c r="C97" s="16" t="s">
@@ -4485,14 +4485,14 @@
       </c>
       <c r="D97" s="184"/>
       <c r="E97" s="22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F97" s="134" t="s">
         <v>35</v>
       </c>
       <c r="G97" s="40"/>
       <c r="H97" s="40" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I97" s="40"/>
       <c r="J97" s="97"/>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="N97" s="27"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="209" t="s">
         <v>5</v>
       </c>
@@ -4526,7 +4526,7 @@
       <c r="N98" s="25"/>
       <c r="O98" s="4"/>
     </row>
-    <row r="99" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="56"/>
       <c r="B99" s="210"/>
       <c r="C99" s="14" t="s">
@@ -4534,27 +4534,27 @@
       </c>
       <c r="D99" s="186"/>
       <c r="E99" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="F99" s="155" t="s">
         <v>164</v>
-      </c>
-      <c r="F99" s="155" t="s">
-        <v>165</v>
       </c>
       <c r="G99" s="156"/>
       <c r="H99" s="156" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I99" s="156"/>
       <c r="J99" s="37" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K99" s="22"/>
       <c r="L99" s="22" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M99" s="26"/>
       <c r="N99" s="25"/>
     </row>
-    <row r="100" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="56"/>
       <c r="B100" s="210"/>
       <c r="C100" s="14" t="s">
@@ -4562,14 +4562,14 @@
       </c>
       <c r="D100" s="154"/>
       <c r="E100" s="26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F100" s="83" t="s">
         <v>35</v>
       </c>
       <c r="G100" s="67"/>
       <c r="H100" s="67" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I100" s="67"/>
       <c r="J100" s="37" t="s">
@@ -4582,7 +4582,7 @@
       <c r="M100" s="61"/>
       <c r="N100" s="25"/>
     </row>
-    <row r="101" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="41"/>
       <c r="B101" s="208"/>
       <c r="C101" s="16" t="s">
@@ -4590,25 +4590,25 @@
       </c>
       <c r="D101" s="184"/>
       <c r="E101" s="26" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F101" s="167" t="s">
         <v>35</v>
       </c>
       <c r="G101" s="159"/>
       <c r="H101" s="158" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I101" s="140"/>
       <c r="J101" s="39" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K101" s="78"/>
       <c r="L101" s="30"/>
       <c r="M101" s="61"/>
       <c r="N101" s="61"/>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="209" t="s">
         <v>7</v>
       </c>
@@ -4628,7 +4628,7 @@
       <c r="M102" s="61"/>
       <c r="N102" s="22"/>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="56"/>
       <c r="B103" s="210"/>
       <c r="C103" s="14" t="s">
@@ -4636,25 +4636,25 @@
       </c>
       <c r="D103" s="172"/>
       <c r="E103" s="22" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F103" s="83"/>
       <c r="G103" s="67"/>
       <c r="H103" s="67" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I103" s="67"/>
       <c r="J103" s="38" t="s">
         <v>141</v>
       </c>
       <c r="K103" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L103" s="15"/>
       <c r="M103" s="27"/>
       <c r="N103" s="25"/>
     </row>
-    <row r="104" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="56"/>
       <c r="B104" s="210"/>
       <c r="C104" s="14" t="s">
@@ -4667,7 +4667,7 @@
       <c r="F104" s="130"/>
       <c r="G104" s="37"/>
       <c r="H104" s="37" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I104" s="173"/>
       <c r="J104" s="98"/>
@@ -4676,7 +4676,7 @@
       <c r="M104" s="22"/>
       <c r="N104" s="65"/>
     </row>
-    <row r="105" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="41"/>
       <c r="B105" s="208"/>
       <c r="C105" s="16"/>
@@ -4692,7 +4692,7 @@
       <c r="M105" s="26"/>
       <c r="N105" s="27"/>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="209" t="s">
         <v>8</v>
       </c>
@@ -4712,7 +4712,7 @@
       <c r="M106" s="26"/>
       <c r="N106" s="22"/>
     </row>
-    <row r="107" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="110"/>
       <c r="B107" s="211"/>
       <c r="C107" s="16"/>
@@ -4728,7 +4728,7 @@
       <c r="M107" s="26"/>
       <c r="N107" s="22"/>
     </row>
-    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="31" t="s">
         <v>9</v>
       </c>
@@ -4736,59 +4736,59 @@
         <v>46126</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D108" s="12"/>
       <c r="E108" s="221" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F108" s="127"/>
       <c r="G108" s="42"/>
       <c r="H108" s="42" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I108" s="42"/>
       <c r="J108" s="46" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K108" s="222">
         <v>3.8</v>
       </c>
       <c r="L108" s="24" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M108" s="22"/>
       <c r="N108" s="21"/>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A109" s="56"/>
       <c r="B109" s="207"/>
       <c r="C109" s="14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D109" s="128"/>
       <c r="E109" s="224" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F109" s="146"/>
       <c r="G109" s="147"/>
       <c r="H109" s="174" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I109" s="147"/>
       <c r="J109" s="40" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K109" s="223">
         <v>3.8</v>
       </c>
       <c r="L109" s="21" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M109" s="22"/>
       <c r="N109" s="57"/>
     </row>
-    <row r="110" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="56"/>
       <c r="B110" s="210"/>
       <c r="C110" s="14"/>
@@ -4804,7 +4804,7 @@
       <c r="M110" s="27"/>
       <c r="N110" s="88"/>
     </row>
-    <row r="111" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="41"/>
       <c r="B111" s="208"/>
       <c r="C111" s="16" t="s">
@@ -4817,25 +4817,25 @@
       <c r="F111" s="175"/>
       <c r="G111" s="78"/>
       <c r="H111" s="78" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I111" s="78"/>
       <c r="J111" s="43" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K111" s="18"/>
       <c r="L111" s="176"/>
       <c r="M111" s="94"/>
       <c r="N111" s="95"/>
     </row>
-    <row r="113" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E113" s="112" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="114" spans="5:5" ht="110.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="5:5" ht="110.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E114" s="113" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -4854,7 +4854,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D8F6E0-B935-4442-A9F9-93EFDE55CF19}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
